--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251102_201040.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251102_201040.xlsx
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251102_201040.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_cobasi_20251102_201040.xlsx
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
